--- a/data/excel/ventas_combustibles.xlsx
+++ b/data/excel/ventas_combustibles.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI201"/>
+  <dimension ref="A1:EI202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -84562,16 +84562,16 @@
         <v>5029.51</v>
       </c>
       <c r="P201" t="n">
-        <v>18762.761</v>
+        <v>25340.761</v>
       </c>
       <c r="Q201" t="n">
-        <v>18762.761</v>
+        <v>25340.761</v>
       </c>
       <c r="R201" t="n">
-        <v>830722.535</v>
+        <v>837300.535</v>
       </c>
       <c r="S201" t="n">
-        <v>817361.975</v>
+        <v>823939.975</v>
       </c>
       <c r="T201" t="n">
         <v>220740</v>
@@ -84778,16 +84778,16 @@
         <v>6707.22</v>
       </c>
       <c r="CJ201" t="n">
-        <v>19174.761</v>
+        <v>25752.761</v>
       </c>
       <c r="CK201" t="n">
-        <v>19174.761</v>
+        <v>25752.761</v>
       </c>
       <c r="CL201" t="n">
-        <v>1180216.614</v>
+        <v>1186794.614</v>
       </c>
       <c r="CM201" t="n">
-        <v>1164272.704</v>
+        <v>1170850.704</v>
       </c>
       <c r="CN201" t="n">
         <v>448740</v>
@@ -84856,7 +84856,7 @@
         <v>39375.85</v>
       </c>
       <c r="DJ201" t="n">
-        <v>101107.996</v>
+        <v>107685.996</v>
       </c>
       <c r="DK201" t="n">
         <v>245751.5</v>
@@ -84916,7 +84916,7 @@
         <v>46969.98</v>
       </c>
       <c r="ED201" t="n">
-        <v>117694.409</v>
+        <v>124272.409</v>
       </c>
       <c r="EE201" t="n">
         <v>774732.847</v>
@@ -84932,6 +84932,425 @@
       </c>
       <c r="EI201" t="n">
         <v>14772.589</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B202" t="n">
+        <v>486958</v>
+      </c>
+      <c r="C202" t="n">
+        <v>482521</v>
+      </c>
+      <c r="D202" t="n">
+        <v>107738</v>
+      </c>
+      <c r="E202" t="n">
+        <v>107738</v>
+      </c>
+      <c r="F202" t="n">
+        <v>159396.28</v>
+      </c>
+      <c r="G202" t="n">
+        <v>152038.15</v>
+      </c>
+      <c r="H202" t="n">
+        <v>55063.7</v>
+      </c>
+      <c r="I202" t="n">
+        <v>55063.7</v>
+      </c>
+      <c r="J202" t="n">
+        <v>15849</v>
+      </c>
+      <c r="K202" t="n">
+        <v>15849</v>
+      </c>
+      <c r="L202" t="n">
+        <v>11320</v>
+      </c>
+      <c r="M202" t="n">
+        <v>11320</v>
+      </c>
+      <c r="N202" t="n">
+        <v>5860.55</v>
+      </c>
+      <c r="O202" t="n">
+        <v>5860.55</v>
+      </c>
+      <c r="P202" t="n">
+        <v>25510.591</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>25510.591</v>
+      </c>
+      <c r="R202" t="n">
+        <v>867696.121</v>
+      </c>
+      <c r="S202" t="n">
+        <v>855900.991</v>
+      </c>
+      <c r="T202" t="n">
+        <v>228432</v>
+      </c>
+      <c r="U202" t="n">
+        <v>228432</v>
+      </c>
+      <c r="V202" t="n">
+        <v>65683</v>
+      </c>
+      <c r="W202" t="n">
+        <v>65565</v>
+      </c>
+      <c r="X202" t="n">
+        <v>38719.11</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>36320.77</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>14768.04</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>14732.1</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>3165</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>3165</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>2370.15</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>2370.15</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>600</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>600</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>356154.3</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>353602.02</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>322016</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>322016</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>124503</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>124503</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>79104.57000000001</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>79104.57000000001</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>36793.43</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>36793.43</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>11074</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>11074</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>9853</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>9853</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>7598.28</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>7598.28</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>1920</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>1920</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>592862.28</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>592862.28</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>125588</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>125588</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>56923</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>56923</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>23220.48</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>23220.48</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>5862.97</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>5862.97</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>927</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>927</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>926</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>926</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>857.1799999999999</v>
+      </c>
+      <c r="BQ202" t="n">
+        <v>857.1799999999999</v>
+      </c>
+      <c r="BR202" t="n">
+        <v>274</v>
+      </c>
+      <c r="BS202" t="n">
+        <v>274</v>
+      </c>
+      <c r="BT202" t="n">
+        <v>214578.63</v>
+      </c>
+      <c r="BU202" t="n">
+        <v>214578.63</v>
+      </c>
+      <c r="BV202" t="n">
+        <v>715390</v>
+      </c>
+      <c r="BW202" t="n">
+        <v>710953</v>
+      </c>
+      <c r="BX202" t="n">
+        <v>173421</v>
+      </c>
+      <c r="BY202" t="n">
+        <v>173303</v>
+      </c>
+      <c r="BZ202" t="n">
+        <v>198115.39</v>
+      </c>
+      <c r="CA202" t="n">
+        <v>188358.92</v>
+      </c>
+      <c r="CB202" t="n">
+        <v>69831.74000000001</v>
+      </c>
+      <c r="CC202" t="n">
+        <v>69795.8</v>
+      </c>
+      <c r="CD202" t="n">
+        <v>19014</v>
+      </c>
+      <c r="CE202" t="n">
+        <v>19014</v>
+      </c>
+      <c r="CF202" t="n">
+        <v>13737</v>
+      </c>
+      <c r="CG202" t="n">
+        <v>13737</v>
+      </c>
+      <c r="CH202" t="n">
+        <v>8230.700000000001</v>
+      </c>
+      <c r="CI202" t="n">
+        <v>8230.700000000001</v>
+      </c>
+      <c r="CJ202" t="n">
+        <v>26110.591</v>
+      </c>
+      <c r="CK202" t="n">
+        <v>26110.591</v>
+      </c>
+      <c r="CL202" t="n">
+        <v>1223850.421</v>
+      </c>
+      <c r="CM202" t="n">
+        <v>1209503.011</v>
+      </c>
+      <c r="CN202" t="n">
+        <v>447604</v>
+      </c>
+      <c r="CO202" t="n">
+        <v>447604</v>
+      </c>
+      <c r="CP202" t="n">
+        <v>181426</v>
+      </c>
+      <c r="CQ202" t="n">
+        <v>181426</v>
+      </c>
+      <c r="CR202" t="n">
+        <v>102325.05</v>
+      </c>
+      <c r="CS202" t="n">
+        <v>102325.05</v>
+      </c>
+      <c r="CT202" t="n">
+        <v>42656.4</v>
+      </c>
+      <c r="CU202" t="n">
+        <v>42656.4</v>
+      </c>
+      <c r="CV202" t="n">
+        <v>12001</v>
+      </c>
+      <c r="CW202" t="n">
+        <v>12001</v>
+      </c>
+      <c r="CX202" t="n">
+        <v>10779</v>
+      </c>
+      <c r="CY202" t="n">
+        <v>10779</v>
+      </c>
+      <c r="CZ202" t="n">
+        <v>8455.459999999999</v>
+      </c>
+      <c r="DA202" t="n">
+        <v>8455.459999999999</v>
+      </c>
+      <c r="DB202" t="n">
+        <v>2194</v>
+      </c>
+      <c r="DC202" t="n">
+        <v>2194</v>
+      </c>
+      <c r="DD202" t="n">
+        <v>807440.91</v>
+      </c>
+      <c r="DE202" t="n">
+        <v>807440.91</v>
+      </c>
+      <c r="DF202" t="n">
+        <v>378053.32</v>
+      </c>
+      <c r="DG202" t="n">
+        <v>92094.53999999999</v>
+      </c>
+      <c r="DH202" t="n">
+        <v>208963.89</v>
+      </c>
+      <c r="DI202" t="n">
+        <v>41893.36</v>
+      </c>
+      <c r="DJ202" t="n">
+        <v>109910.341</v>
+      </c>
+      <c r="DK202" t="n">
+        <v>248068.47</v>
+      </c>
+      <c r="DL202" t="n">
+        <v>50732.9</v>
+      </c>
+      <c r="DM202" t="n">
+        <v>24103.96</v>
+      </c>
+      <c r="DN202" t="n">
+        <v>8445.08</v>
+      </c>
+      <c r="DO202" t="n">
+        <v>16090.58</v>
+      </c>
+      <c r="DP202" t="n">
+        <v>570687.77</v>
+      </c>
+      <c r="DQ202" t="n">
+        <v>6284.34</v>
+      </c>
+      <c r="DR202" t="n">
+        <v>1619.51</v>
+      </c>
+      <c r="DS202" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DT202" t="n">
+        <v>14161.52</v>
+      </c>
+      <c r="DU202" t="n">
+        <v>207046.86</v>
+      </c>
+      <c r="DV202" t="n">
+        <v>6158.69</v>
+      </c>
+      <c r="DW202" t="n">
+        <v>237.82</v>
+      </c>
+      <c r="DX202" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DY202" t="n">
+        <v>1086.22</v>
+      </c>
+      <c r="DZ202" t="n">
+        <v>626121.79</v>
+      </c>
+      <c r="EA202" t="n">
+        <v>142827.44</v>
+      </c>
+      <c r="EB202" t="n">
+        <v>233067.85</v>
+      </c>
+      <c r="EC202" t="n">
+        <v>50338.44</v>
+      </c>
+      <c r="ED202" t="n">
+        <v>126000.921</v>
+      </c>
+      <c r="EE202" t="n">
+        <v>777734.63</v>
+      </c>
+      <c r="EF202" t="n">
+        <v>12443.03</v>
+      </c>
+      <c r="EG202" t="n">
+        <v>1857.33</v>
+      </c>
+      <c r="EH202" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="EI202" t="n">
+        <v>15247.74</v>
       </c>
     </row>
   </sheetData>
@@ -84992,7 +85411,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.energia.gob.ar/contenidos/archivos/Reorganizacion/informacion_del_mercado/mercado_hidrocarburos/tablas_dinamicas/dowstream/individuales/TD_ventas_mercado.zip https://www.energia.gob.ar/contenidos/archivos/Reorganizacion/informacion_del_mercado/mercado_hidrocarburos/tablas_dinamicas/dowstream/individuales/TD_ventas_mercado_2010_2019.zip</t>
+          <t>https://www.energia.gob.ar/contenidos/archivos/Reorganizacion/informacion_del_mercado/mercado_hidrocarburos/tablas_dinamicas/dowstream/individuales/TD_ventas_mercado.zip</t>
         </is>
       </c>
     </row>
@@ -85004,7 +85423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T13:57:24Z</t>
+          <t>2026-10-24T05:02:43Z</t>
         </is>
       </c>
     </row>
@@ -85016,7 +85435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
